--- a/artfynd/A 34876-2021 artfynd.xlsx
+++ b/artfynd/A 34876-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34876-2021 artfynd.xlsx
+++ b/artfynd/A 34876-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102126371</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386854.4396338332</v>
+        <v>386854</v>
       </c>
       <c r="R2" t="n">
-        <v>6685389.516594362</v>
+        <v>6685390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,211 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102126375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89292</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>510</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hovfjället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>386810</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6685387</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109779136</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnkärret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387031</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6685228</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emelie Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emelie Andersson, Erik Löfroth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
